--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="178">
   <si>
     <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
   </si>
@@ -265,6 +265,33 @@
     <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
   </si>
   <si>
+    <t>hightech</t>
+  </si>
+  <si>
+    <t>这个高科技的名字</t>
+  </si>
+  <si>
+    <t>高科技的效果</t>
+  </si>
+  <si>
+    <t>timeCostBase</t>
+  </si>
+  <si>
+    <t>升级高科技需要的基础时间</t>
+  </si>
+  <si>
+    <t>timeCostMutiple</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>通过第几关后解锁</t>
+  </si>
+  <si>
+    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
+  </si>
+  <si>
     <t>如上</t>
   </si>
   <si>
@@ -488,6 +515,57 @@
   </si>
   <si>
     <t>死亡时后退距离</t>
+  </si>
+  <si>
+    <t>hightechLimit</t>
+  </si>
+  <si>
+    <t>同时研发的高科技数量</t>
+  </si>
+  <si>
+    <t>offlineMax</t>
+  </si>
+  <si>
+    <t>离线时长(h）</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>这个神器的名字</t>
+  </si>
+  <si>
+    <t>神器的效果</t>
+  </si>
+  <si>
+    <t>界面上的描述</t>
+  </si>
+  <si>
+    <t>升级神器需要的基础时间</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>可变参数，具体效果参看神器的效果des</t>
+  </si>
+  <si>
+    <t>超时空炼铁炉</t>
+  </si>
+  <si>
+    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，向上取整，点击获取，10秒后消失</t>
+  </si>
+  <si>
+    <t>正电子聚焦装置</t>
+  </si>
+  <si>
+    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）向上取整.</t>
+  </si>
+  <si>
+    <t>简并态装甲</t>
+  </si>
+  <si>
+    <t>armour当前值增加（1+para1*等级），向上取整。</t>
   </si>
 </sst>
 </file>
@@ -1103,8 +1181,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1424,8 +1505,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -1451,32 +1532,32 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <v>0.5</v>
@@ -1484,10 +1565,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -1495,10 +1576,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C7">
         <v>0.5</v>
@@ -1506,13 +1587,35 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C8">
         <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -2,17 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="0" firstSheet="0"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="config" sheetId="6" r:id="rId7" state="visible"/>
+    <sheet name="config" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,222 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="178">
-  <si>
-    <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
-  </si>
-  <si>
-    <t>战舰会自动使用武器，攻击敌方飞行器，武器有各种参数，在武器表里定义</t>
-  </si>
-  <si>
-    <t>在每个关卡，敌方飞行器每隔一段距离就会出现。全部击落后才能前进，战斗时无法移动。关卡最后出现一个敌方BOSS飞行器，击毁后通关</t>
-  </si>
-  <si>
-    <t>敌方飞行器有各种参数，在怪物表里配置。怪物群负责整理一整群怪物，而关卡表将配置怪物群，用来辨别哪些敌方飞行器将出现在关卡里及出现在关卡的什么位置</t>
-  </si>
-  <si>
-    <t>敌方飞行器被击毁后会掉落资源，鼠标划过可以拾取。如果一段时间没有拾取，则自动拾取，但会有损耗，损耗比例在config里配置</t>
-  </si>
-  <si>
-    <t>飞行器初始武器为激光，激光会发射一道光束，攻击一个目标。</t>
-  </si>
-  <si>
-    <t>第二个武器为导弹，导弹在通关第一关后获得，导弹会同时发射3枚导弹，锁定3个敌人（若不足则只发射对应数量的导弹）</t>
-  </si>
-  <si>
-    <t>玩家可以选择任何一个已经通关过的关卡重新通关，或者无限循环该关卡。如果选择循环，则击败BOSS后就从这关开始重新前进</t>
-  </si>
-  <si>
-    <t>具体配置如下，表格均从第四行开始是实际配置</t>
-  </si>
-  <si>
-    <t>表格名</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>列名</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>关卡的id</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>关卡长度</t>
-  </si>
-  <si>
-    <t>monGroup</t>
-  </si>
-  <si>
-    <t>怪物群id</t>
-  </si>
-  <si>
-    <t>格式为{id|比例，id|比例....}，id为monGroup表的id，比例表示在关卡长度的%多少处出现</t>
-  </si>
-  <si>
-    <t>atkRatio</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的器伤害*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>所有倍率，在关卡中由上一关的倍率线性成长到本关倍率。如第一关倍率是1，第二关倍率是10，则10%的长度时是2..以此类推</t>
-  </si>
-  <si>
-    <t>lifeRatio</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的生命*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>resRatio</t>
-  </si>
-  <si>
-    <t>资源倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器摧毁时获得的资源乘该值</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>武器名</t>
-  </si>
-  <si>
     <t>des</t>
   </si>
   <si>
-    <t>武器说明</t>
-  </si>
-  <si>
-    <t>武器等级</t>
-  </si>
-  <si>
-    <t>dmg</t>
-  </si>
-  <si>
-    <t>武器命中时的伤害</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>武器发射需要的时间</t>
-  </si>
-  <si>
-    <t>unlock</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器</t>
-  </si>
-  <si>
-    <t>res_1</t>
-  </si>
-  <si>
-    <t>升级该武器需要的资源</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为res_x。如res_2，res_3就表示第二种，第三种资源。资源为res表的id</t>
-  </si>
-  <si>
-    <t>cost_1</t>
-  </si>
-  <si>
-    <t>升到该等级需要的资源数量</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为cost_x。如cost_2，cost_3就表示第二种，第三种资源消耗量。与res_x一一对应</t>
-  </si>
-  <si>
-    <t>para1</t>
-  </si>
-  <si>
-    <t>武器的额外参数。具体每个武器再定义，一般可参考des</t>
-  </si>
-  <si>
-    <t>mon</t>
-  </si>
-  <si>
-    <t>敌方飞行器id</t>
-  </si>
-  <si>
-    <t>飞行器描述</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的</t>
-  </si>
-  <si>
-    <t>dmgMultiple</t>
-  </si>
-  <si>
-    <t>武器的伤害乘该值，这样计算完后的就是这个飞行器的伤害</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>飞行器生命</t>
-  </si>
-  <si>
-    <t>res</t>
-  </si>
-  <si>
-    <t>掉落的资源</t>
-  </si>
-  <si>
-    <t>格式为｛id，数量，概率｝，id为res表的id，数量就是掉出来的数量，概率是被击毁时有多大概率掉落该资源</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>大小</t>
-  </si>
-  <si>
-    <t>战场中占据的格子数</t>
-  </si>
-  <si>
-    <t>敌方飞行器组id</t>
-  </si>
-  <si>
-    <t>飞行器组描述</t>
-  </si>
-  <si>
-    <t>格式为{id1，id2....｝</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置</t>
-  </si>
-  <si>
-    <t>资源id</t>
-  </si>
-  <si>
-    <t>资源名</t>
-  </si>
-  <si>
-    <t>config</t>
+    <t>para_1</t>
   </si>
   <si>
     <t>这个配置的名字</t>
@@ -256,234 +44,12 @@
     <t>配置的描述</t>
   </si>
   <si>
-    <t>para_1</t>
-  </si>
-  <si>
     <t>配置的参数</t>
   </si>
   <si>
-    <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
-  </si>
-  <si>
-    <t>hightech</t>
-  </si>
-  <si>
-    <t>这个高科技的名字</t>
-  </si>
-  <si>
-    <t>高科技的效果</t>
-  </si>
-  <si>
-    <t>timeCostBase</t>
-  </si>
-  <si>
-    <t>升级高科技需要的基础时间</t>
-  </si>
-  <si>
-    <t>timeCostMutiple</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>通过第几关后解锁</t>
-  </si>
-  <si>
-    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
-  </si>
-  <si>
     <t>如上</t>
   </si>
   <si>
-    <t>{2|0.1，2|0.2，2|0.3，2|0.4，2|0.5，2|0.6，2|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，8|0.9}</t>
-  </si>
-  <si>
-    <t>dmgtype</t>
-  </si>
-  <si>
-    <t>res_2</t>
-  </si>
-  <si>
-    <t>cost_2</t>
-  </si>
-  <si>
-    <t>para2</t>
-  </si>
-  <si>
-    <t>para3</t>
-  </si>
-  <si>
-    <t>伤害类型，1为能量，2为物理。</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器。不填则这行无意义</t>
-  </si>
-  <si>
-    <t>armour</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础生命，如果没了，飞船就会爆炸！然后后退。额外参数para1是生命值，dmgtype表明护甲对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础护盾，护盾会先于护甲被扣除，同时护盾会缓慢恢复。额外参数para1是护盾值，para2是每秒恢复的比例，para3是连续多少秒不受攻击后才开始恢复，被攻击会立即停止恢复，dmgtype表明护盾对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>laser</t>
-  </si>
-  <si>
-    <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>missile</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发。para2是导弹飞行速度</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发</t>
-  </si>
-  <si>
-    <t>cannon</t>
-  </si>
-  <si>
-    <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>laser_mon</t>
-  </si>
-  <si>
-    <t>missile-mon</t>
-  </si>
-  <si>
-    <t>cannon-mon</t>
-  </si>
-  <si>
-    <t>armourType</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的,格式为｛name|数量，name|数量...}</t>
-  </si>
-  <si>
-    <t>护甲类型</t>
-  </si>
-  <si>
-    <t>1为能量，2为物理</t>
-  </si>
-  <si>
-    <t>激光飞船</t>
-  </si>
-  <si>
-    <t>｛laser_mon|1｝</t>
-  </si>
-  <si>
-    <t>{1,10,0.5}</t>
-  </si>
-  <si>
-    <t>火炮飞船</t>
-  </si>
-  <si>
-    <t>｛cannon-mon|1｝</t>
-  </si>
-  <si>
-    <t>激光飞船-弱</t>
-  </si>
-  <si>
-    <t>{1,5,0.2}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛laser_mon|2,cannon-mon|2｝</t>
-  </si>
-  <si>
-    <t>{2,1,1}</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗能量</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置，null表示此处无飞船｝</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，1，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，2，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>基础飞船组</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>激光飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，3，3，3，3，3，3，null，null}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，4，4，4，4，4，4，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，5，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗能量</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，6，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-双BOSS</t>
-  </si>
-  <si>
-    <t>｛null，null，null，5，null，null，6，null，null，null}</t>
-  </si>
-  <si>
-    <t>铁</t>
-  </si>
-  <si>
-    <t>铝</t>
-  </si>
-  <si>
     <t>startEquip</t>
   </si>
   <si>
@@ -529,43 +95,13 @@
     <t>离线时长(h）</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>这个神器的名字</t>
-  </si>
-  <si>
-    <t>神器的效果</t>
-  </si>
-  <si>
-    <t>界面上的描述</t>
-  </si>
-  <si>
-    <t>升级神器需要的基础时间</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>可变参数，具体效果参看神器的效果des</t>
-  </si>
-  <si>
-    <t>超时空炼铁炉</t>
-  </si>
-  <si>
-    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，向上取整，点击获取，10秒后消失</t>
-  </si>
-  <si>
-    <t>正电子聚焦装置</t>
-  </si>
-  <si>
-    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）向上取整.</t>
-  </si>
-  <si>
-    <t>简并态装甲</t>
-  </si>
-  <si>
-    <t>armour当前值增加（1+para1*等级），向上取整。</t>
+    <t>autoGenRes</t>
+  </si>
+  <si>
+    <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
+  </si>
+  <si>
+    <t>10,2,10,40</t>
   </si>
 </sst>
 </file>
@@ -1181,18 +717,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1502,62 +1029,65 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="13.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>0.5</v>
@@ -1565,21 +1095,21 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>0.5</v>
@@ -1587,10 +1117,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>300</v>
@@ -1598,10 +1128,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1609,13 +1139,24 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="C10">
         <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="6" r:id="rId1"/>
@@ -101,7 +106,7 @@
     <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
   </si>
   <si>
-    <t>10,2,10,40</t>
+    <t>30,2,5,40</t>
   </si>
 </sst>
 </file>
@@ -1033,9 +1038,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
+    <col min="1" max="1" width="13.3796296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1123,7 +1128,7 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:3">

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="6" r:id="rId1"/>
@@ -32,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>name</t>
   </si>
@@ -88,25 +83,40 @@
     <t>死亡时后退距离</t>
   </si>
   <si>
+    <t>offlineMax</t>
+  </si>
+  <si>
+    <t>离线时长(h）</t>
+  </si>
+  <si>
+    <t>autoGenRes</t>
+  </si>
+  <si>
+    <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
+  </si>
+  <si>
+    <t>30,2,5,40</t>
+  </si>
+  <si>
+    <t>scientistCost</t>
+  </si>
+  <si>
+    <t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</t>
+  </si>
+  <si>
+    <t>1.3,1|100,2|10</t>
+  </si>
+  <si>
     <t>hightechLimit</t>
   </si>
   <si>
-    <t>同时研发的高科技数量</t>
-  </si>
-  <si>
-    <t>offlineMax</t>
-  </si>
-  <si>
-    <t>离线时长(h）</t>
-  </si>
-  <si>
-    <t>autoGenRes</t>
-  </si>
-  <si>
-    <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
-  </si>
-  <si>
-    <t>30,2,5,40</t>
+    <t>高科技投入科学家的科研点数衰减</t>
+  </si>
+  <si>
+    <t>techPointGet</t>
+  </si>
+  <si>
+    <t>高科技点数获取</t>
   </si>
 </sst>
 </file>
@@ -1037,10 +1047,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="13.3796296296296" customWidth="1"/>
+    <col min="1" max="1" width="13.3833333333333" customWidth="1"/>
+    <col min="13" max="14" width="12.625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1139,7 +1150,7 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1149,19 +1160,41 @@
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10">
-        <v>4</v>
+      <c r="C10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>name</t>
   </si>
@@ -117,6 +117,39 @@
   </si>
   <si>
     <t>高科技点数获取</t>
+  </si>
+  <si>
+    <t>jewelDropLevel</t>
+  </si>
+  <si>
+    <t>宝石开始掉落的关卡</t>
+  </si>
+  <si>
+    <t>jewelDrop</t>
+  </si>
+  <si>
+    <t>宝石碎片掉率</t>
+  </si>
+  <si>
+    <t>jewelCombine</t>
+  </si>
+  <si>
+    <t>宝石合成需要数量</t>
+  </si>
+  <si>
+    <t>baseCriDmg</t>
+  </si>
+  <si>
+    <t>基础暴击伤害</t>
+  </si>
+  <si>
+    <t>equipmentSocket</t>
+  </si>
+  <si>
+    <t>装备多少级有多少个插槽.格式为等级|插槽数,等级|插槽数...</t>
+  </si>
+  <si>
+    <t>1|1,20|2,40|3</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.3833333333333" customWidth="1"/>
@@ -1197,6 +1230,61 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>name</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>宝石合成需要数量</t>
+  </si>
+  <si>
+    <t>jewelCompose</t>
+  </si>
+  <si>
+    <t>宝石分解资源,资源id|数量</t>
+  </si>
+  <si>
+    <t>1|1000</t>
   </si>
   <si>
     <t>baseCriDmg</t>
@@ -1080,7 +1089,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.3833333333333" customWidth="1"/>
@@ -1270,19 +1279,30 @@
       <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="C17">
-        <v>2</v>
+      <c r="C17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" t="s">
         <v>40</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>name</t>
   </si>
@@ -137,13 +137,10 @@
     <t>宝石合成需要数量</t>
   </si>
   <si>
-    <t>jewelCompose</t>
-  </si>
-  <si>
-    <t>宝石分解资源,资源id|数量</t>
-  </si>
-  <si>
-    <t>1|1000</t>
+    <t>jewelCreat</t>
+  </si>
+  <si>
+    <t>宝石生成需要碎片</t>
   </si>
   <si>
     <t>baseCriDmg</t>
@@ -1279,16 +1276,16 @@
       <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="C17" t="s">
-        <v>38</v>
+      <c r="C17">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1296,13 +1293,13 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
         <v>41</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1236,17 +1236,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14">
-        <v>8</v>
-      </c>
-    </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>32</v>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1510,6 +1510,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hightechCostGrowthLevel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>高科技耗时指数增长阈值，当前等级超过此值后生效</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>400</v>
+      </c>
+    </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>30</v>

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>400</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1003,657 +1003,672 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
-  <cols>
-    <col width="48" customWidth="1" style="1" min="1" max="1"/>
-    <col width="42" customWidth="1" style="1" min="2" max="2"/>
-    <col width="49" customWidth="1" style="1" min="3" max="3"/>
-    <col width="12.62963008880615" customWidth="1" style="1" min="13" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>des</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>para_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>这个配置的名字</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>配置的描述</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>配置的参数</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>如上</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>如上</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>如上</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>startEquip</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>armour,laser</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>dmgReduce</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>护甲类型对应时，减少的伤害</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>movement</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>飞船的移动速度，单位是秒</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>autoCollectReduce</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>自动拾取时的损耗</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>backRange</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>死亡时后退距离</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>offlineMax</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>离线时长(h）</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>autoGenRes</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>30,2,5,40</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>scientistCost</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>1.2,1|100,2|5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>hightechLimit</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>高科技投入AI的科研点数衰减</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>techPointGet</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>高科技点数获取</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>hightechCostGrowthLevel</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>高科技耗时指数增长阈值，当前等级超过此值后生效</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>jewelDrop</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>宝石碎片掉率</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>chronoParticlesPerSecond</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>每离线秒获得的超时空微粒</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>chronoDefaultSpeed</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>进入游戏及微粒不足时恢复的倍率</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>chronoSpeeds</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>倍率|每现实秒微粒消耗，逗号分隔</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>1|0,2|1,3|2,4|3,5|4,6|5,7|6,8|7,9|8,10|9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>reactorEnergyBase</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>反应炉1级总能源</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>reactorEnergyGrowth</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>反应炉每级总能源倍率</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="n">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>reactorUpgradeBase</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>反应炉1级升级铀消耗</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>reactorUpgradeGrowth</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>反应炉每级升级费用倍率</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>reactorBoostExponent</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>模块能源提升指数；提升百分比为分配能源的该次幂</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>reactorUraniumId</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>反应炉升级消耗的资源ID</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t>reactorModules</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t>反应炉可分配模块ID，逗号分隔</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>weapons,defence,smelting,condensation</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>reactorInitialLevel</t>
-        </is>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t>新存档反应炉初始等级</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t>reactorPercentScale</t>
-        </is>
-      </c>
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t>提升百分比换算分母</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t>reactorAllocationStep</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>能源滑杆最小步长</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="n"/>
-      <c r="B29" s="0" t="n"/>
-      <c r="C29" s="0" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="n"/>
-      <c r="B30" s="0" t="n"/>
-      <c r="C30" s="0" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t>playerVisualScaleFrigate</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>我方护卫舰显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t>playerVisualScaleDestroyer</t>
-        </is>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t>我方驱逐舰显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t>playerVisualScaleCruiser</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>我方巡洋舰显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1" s="1">
-      <c r="A34" s="0" t="inlineStr">
-        <is>
-          <t>playerVisualScaleBattleship</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>我方战列舰显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1" s="1">
-      <c r="A35" s="0" t="inlineStr">
-        <is>
-          <t>playerVisualScaleHeavy_Battleship</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>我方重型战列舰显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1" s="1">
-      <c r="A36" s="0" t="inlineStr">
-        <is>
-          <t>enemyVisualScaleSize1</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>敌方 size 1 显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" s="1">
-      <c r="A37" s="0" t="inlineStr">
-        <is>
-          <t>enemyVisualScaleSize2</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>敌方 size 2 显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" s="1">
-      <c r="A38" s="0" t="inlineStr">
-        <is>
-          <t>enemyVisualScaleSize3</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>敌方 size 3 显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1" s="1">
-      <c r="A39" s="0" t="inlineStr">
-        <is>
-          <t>enemyVisualScaleSize4</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>敌方 size 4 显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1" s="1">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>enemyVisualScaleSize5</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>敌方 size 5 显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1" s="1">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t>enemyVisualScaleSize6</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>敌方 size 6 显示倍率，仅影响舰体贴图</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1" s="1">
-      <c r="A42" s="0" t="n"/>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="0" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1" s="1">
-      <c r="A43" s="0" t="n"/>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="0" t="n"/>
-    </row>
-    <row r="44" ht="30" customHeight="1" s="1">
-      <c r="A44" s="0" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="0" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1" s="1">
-      <c r="A45" s="0" t="n"/>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="0" t="n"/>
-    </row>
-    <row r="46" ht="30" customHeight="1" s="1">
-      <c r="A46" s="0" t="n"/>
-      <c r="B46" s="0" t="n"/>
-      <c r="C46" s="0" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:C47"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
+  <ns0:cols>
+    <ns0:col width="48" customWidth="1" style="1" min="1" max="1"/>
+    <ns0:col width="42" customWidth="1" style="1" min="2" max="2"/>
+    <ns0:col width="49" customWidth="1" style="1" min="3" max="3"/>
+    <ns0:col width="12.62963008880615" customWidth="1" style="1" min="13" max="14"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>name</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>des</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>para_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>这个配置的名字</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>配置的描述</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>配置的参数</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>如上</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>如上</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>如上</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>startEquip</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>armour,laser</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>dmgReduce</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>护甲类型对应时，减少的伤害</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" s="0" t="n">
+        <ns0:v>0.5</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>movement</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>飞船的移动速度，单位是秒</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" s="0" t="n">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>autoCollectReduce</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B7" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>自动拾取时的损耗</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" s="0" t="n">
+        <ns0:v>0.5</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>backRange</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B8" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>死亡时后退距离</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" s="0" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>offlineMax</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B9" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>离线时长(h）</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C9" s="0" t="n">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>autoGenRes</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B10" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C10" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>30,2,5,40</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>scientistCost</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B11" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C11" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1.2,1|100,2|5</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>hightechLimit</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B12" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高科技投入AI的科研点数衰减</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C12" s="0" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>techPointGet</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B13" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高科技点数获取</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C13" s="0" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>hightechCostGrowthLevel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B14" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高科技耗时指数增长阈值，当前等级超过此值后生效</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C14" s="0" t="n">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>jewelDrop</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B15" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>宝石碎片掉率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C15" s="0" t="n">
+        <ns0:v>0.2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>chronoParticlesPerSecond</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B16" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>每离线秒获得的超时空微粒</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C16" s="0" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>chronoDefaultSpeed</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B17" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>进入游戏及微粒不足时恢复的倍率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C17" s="0" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>chronoSpeeds</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B18" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>倍率|每现实秒微粒消耗，逗号分隔</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C18" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1|0,2|1,3|2,4|3,5|4,6|5,7|6,8|7,9|8,10|9</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorEnergyBase</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B19" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>反应炉1级总能源</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C19" s="0" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorEnergyGrowth</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B20" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>反应炉每级总能源倍率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C20" s="0" t="n">
+        <ns0:v>1.06</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="A21" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorUpgradeBase</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B21" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>反应炉1级升级铀消耗</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C21" s="0" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorUpgradeGrowth</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B22" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>反应炉每级升级费用倍率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C22" s="0" t="n">
+        <ns0:v>1.35</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorBoostExponent</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B23" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>模块能源提升指数；提升百分比为分配能源的该次幂</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C23" s="0" t="n">
+        <ns0:v>0.8</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorUraniumId</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B24" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>反应炉升级消耗的资源ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C24" s="0" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorModules</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B25" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>反应炉可分配模块ID，逗号分隔</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C25" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>weapons,defence,smelting,condensation</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorInitialLevel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B26" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>新存档反应炉初始等级</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C26" s="0" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorPercentScale</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B27" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>提升百分比换算分母</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C27" s="0" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reactorAllocationStep</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B28" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>能源滑杆最小步长</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C28" s="0" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="29">
+      <ns0:c r="A29" s="0" t="n"/>
+      <ns0:c r="B29" s="0" t="n"/>
+      <ns0:c r="C29" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="30">
+      <ns0:c r="A30" s="0" t="n"/>
+      <ns0:c r="B30" s="0" t="n"/>
+      <ns0:c r="C30" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>playerVisualScaleFrigate</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B31" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>我方护卫舰显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C31" s="0" t="n">
+        <ns0:v>1.3</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="32">
+      <ns0:c r="A32" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>playerVisualScaleDestroyer</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B32" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>我方驱逐舰显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C32" s="0" t="n">
+        <ns0:v>1.1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="33">
+      <ns0:c r="A33" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>playerVisualScaleCruiser</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B33" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>我方巡洋舰显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C33" s="0" t="n">
+        <ns0:v>1.2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="34" ht="30" customHeight="1" s="1">
+      <ns0:c r="A34" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>playerVisualScaleBattleship</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B34" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>我方战列舰显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C34" s="0" t="n">
+        <ns0:v>1.3</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="35" ht="30" customHeight="1" s="1">
+      <ns0:c r="A35" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>playerVisualScaleHeavy_Battleship</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B35" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>我方重型战列舰显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C35" s="0" t="n">
+        <ns0:v>1.4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="36" ht="30" customHeight="1" s="1">
+      <ns0:c r="A36" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>enemyVisualScaleSize1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B36" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方 size 1 显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C36" s="0" t="n">
+        <ns0:v>1.2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="37" ht="30" customHeight="1" s="1">
+      <ns0:c r="A37" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>enemyVisualScaleSize2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B37" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方 size 2 显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C37" s="0" t="n">
+        <ns0:v>1.2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="38" ht="30" customHeight="1" s="1">
+      <ns0:c r="A38" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>enemyVisualScaleSize3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B38" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方 size 3 显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C38" s="0" t="n">
+        <ns0:v>1.4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="39" ht="30" customHeight="1" s="1">
+      <ns0:c r="A39" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>enemyVisualScaleSize4</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B39" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方 size 4 显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C39" s="0" t="n">
+        <ns0:v>1.5</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="40" ht="30" customHeight="1" s="1">
+      <ns0:c r="A40" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>enemyVisualScaleSize5</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B40" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方 size 5 显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C40" s="0" t="n">
+        <ns0:v>1.5</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="41" ht="30" customHeight="1" s="1">
+      <ns0:c r="A41" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>enemyVisualScaleSize6</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B41" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方 size 6 显示倍率，仅影响舰体贴图</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C41" s="0" t="n">
+        <ns0:v>1.7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="42" ht="30" customHeight="1" s="1">
+      <ns0:c r="A42" s="0" t="n"/>
+      <ns0:c r="B42" s="2" t="n"/>
+      <ns0:c r="C42" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="43" ht="30" customHeight="1" s="1">
+      <ns0:c r="A43" s="0" t="n"/>
+      <ns0:c r="B43" s="2" t="n"/>
+      <ns0:c r="C43" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="44" ht="30" customHeight="1" s="1">
+      <ns0:c r="A44" s="0" t="n"/>
+      <ns0:c r="B44" s="2" t="n"/>
+      <ns0:c r="C44" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="45" ht="30" customHeight="1" s="1">
+      <ns0:c r="A45" s="0" t="n"/>
+      <ns0:c r="B45" s="2" t="n"/>
+      <ns0:c r="C45" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="46" ht="30" customHeight="1" s="1">
+      <ns0:c r="A46" s="0" t="n"/>
+      <ns0:c r="B46" s="0" t="n"/>
+      <ns0:c r="C46" s="0" t="n"/>
+    </ns0:row>
+    <ns0:row r="47">
+      <ns0:c r="A47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>explicitEnemyPlayerMinGap</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>显式超空间阵型与玩家舰体包络的最小发射空白，按战场高度比例；不改变普通阵型、船体尺寸或战斗数值。</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C47">
+        <ns0:v>0.12</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</ns0:worksheet>
 </file>
--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1003,672 +1003,672 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:C47"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
-  <ns0:cols>
-    <ns0:col width="48" customWidth="1" style="1" min="1" max="1"/>
-    <ns0:col width="42" customWidth="1" style="1" min="2" max="2"/>
-    <ns0:col width="49" customWidth="1" style="1" min="3" max="3"/>
-    <ns0:col width="12.62963008880615" customWidth="1" style="1" min="13" max="14"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>des</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>para_1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>这个配置的名字</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>配置的描述</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>配置的参数</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>如上</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>如上</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C3" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>如上</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>startEquip</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>armour,laser</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>dmgReduce</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>护甲类型对应时，减少的伤害</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C5" s="0" t="n">
-        <ns0:v>0.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>movement</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>飞船的移动速度，单位是秒</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C6" s="0" t="n">
-        <ns0:v>50</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>autoCollectReduce</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B7" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>自动拾取时的损耗</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C7" s="0" t="n">
-        <ns0:v>0.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>backRange</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B8" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>死亡时后退距离</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C8" s="0" t="n">
-        <ns0:v>200</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>offlineMax</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B9" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>离线时长(h）</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C9" s="0" t="n">
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>autoGenRes</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B10" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C10" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>30,2,5,40</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11">
-      <ns0:c r="A11" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>scientistCost</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B11" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C11" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>1.2,1|100,2|5</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12">
-      <ns0:c r="A12" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>hightechLimit</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B12" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>高科技投入AI的科研点数衰减</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C12" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13">
-      <ns0:c r="A13" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>techPointGet</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B13" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>高科技点数获取</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C13" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14">
-      <ns0:c r="A14" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>hightechCostGrowthLevel</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B14" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>高科技耗时指数增长阈值，当前等级超过此值后生效</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C14" s="0" t="n">
-        <ns0:v>50</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15">
-      <ns0:c r="A15" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>jewelDrop</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B15" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>宝石碎片掉率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C15" s="0" t="n">
-        <ns0:v>0.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16">
-      <ns0:c r="A16" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>chronoParticlesPerSecond</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B16" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>每离线秒获得的超时空微粒</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C16" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17">
-      <ns0:c r="A17" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>chronoDefaultSpeed</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B17" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>进入游戏及微粒不足时恢复的倍率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C17" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18">
-      <ns0:c r="A18" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>chronoSpeeds</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B18" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>倍率|每现实秒微粒消耗，逗号分隔</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C18" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>1|0,2|1,3|2,4|3,5|4,6|5,7|6,8|7,9|8,10|9</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19">
-      <ns0:c r="A19" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorEnergyBase</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B19" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉1级总能源</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C19" s="0" t="n">
-        <ns0:v>100</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20">
-      <ns0:c r="A20" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorEnergyGrowth</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B20" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉每级总能源倍率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C20" s="0" t="n">
-        <ns0:v>1.06</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21">
-      <ns0:c r="A21" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorUpgradeBase</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B21" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉1级升级铀消耗</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C21" s="0" t="n">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22">
-      <ns0:c r="A22" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorUpgradeGrowth</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B22" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉每级升级费用倍率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C22" s="0" t="n">
-        <ns0:v>1.35</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23">
-      <ns0:c r="A23" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorBoostExponent</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B23" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>模块能源提升指数；提升百分比为分配能源的该次幂</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C23" s="0" t="n">
-        <ns0:v>0.8</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24">
-      <ns0:c r="A24" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorUraniumId</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B24" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉升级消耗的资源ID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C24" s="0" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25">
-      <ns0:c r="A25" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorModules</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B25" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉可分配模块ID，逗号分隔</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C25" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>weapons,defence,smelting,condensation</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26">
-      <ns0:c r="A26" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorInitialLevel</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B26" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>新存档反应炉初始等级</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C26" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="27">
-      <ns0:c r="A27" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorPercentScale</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B27" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>提升百分比换算分母</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C27" s="0" t="n">
-        <ns0:v>100</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="28">
-      <ns0:c r="A28" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorAllocationStep</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B28" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>能源滑杆最小步长</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C28" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="29">
-      <ns0:c r="A29" s="0" t="n"/>
-      <ns0:c r="B29" s="0" t="n"/>
-      <ns0:c r="C29" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="30">
-      <ns0:c r="A30" s="0" t="n"/>
-      <ns0:c r="B30" s="0" t="n"/>
-      <ns0:c r="C30" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="31">
-      <ns0:c r="A31" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleFrigate</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B31" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方护卫舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C31" s="0" t="n">
-        <ns0:v>1.3</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="32">
-      <ns0:c r="A32" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleDestroyer</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B32" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方驱逐舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C32" s="0" t="n">
-        <ns0:v>1.1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="33">
-      <ns0:c r="A33" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleCruiser</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B33" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方巡洋舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C33" s="0" t="n">
-        <ns0:v>1.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="34" ht="30" customHeight="1" s="1">
-      <ns0:c r="A34" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleBattleship</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B34" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方战列舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C34" s="0" t="n">
-        <ns0:v>1.3</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="35" ht="30" customHeight="1" s="1">
-      <ns0:c r="A35" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleHeavy_Battleship</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B35" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方重型战列舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C35" s="0" t="n">
-        <ns0:v>1.4</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="36" ht="30" customHeight="1" s="1">
-      <ns0:c r="A36" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B36" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 1 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C36" s="0" t="n">
-        <ns0:v>1.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="37" ht="30" customHeight="1" s="1">
-      <ns0:c r="A37" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize2</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B37" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 2 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C37" s="0" t="n">
-        <ns0:v>1.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="38" ht="30" customHeight="1" s="1">
-      <ns0:c r="A38" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize3</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B38" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 3 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C38" s="0" t="n">
-        <ns0:v>1.4</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="39" ht="30" customHeight="1" s="1">
-      <ns0:c r="A39" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize4</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B39" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 4 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C39" s="0" t="n">
-        <ns0:v>1.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="40" ht="30" customHeight="1" s="1">
-      <ns0:c r="A40" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize5</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B40" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 5 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C40" s="0" t="n">
-        <ns0:v>1.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="41" ht="30" customHeight="1" s="1">
-      <ns0:c r="A41" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize6</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B41" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 6 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C41" s="0" t="n">
-        <ns0:v>1.7</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="42" ht="30" customHeight="1" s="1">
-      <ns0:c r="A42" s="0" t="n"/>
-      <ns0:c r="B42" s="2" t="n"/>
-      <ns0:c r="C42" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="43" ht="30" customHeight="1" s="1">
-      <ns0:c r="A43" s="0" t="n"/>
-      <ns0:c r="B43" s="2" t="n"/>
-      <ns0:c r="C43" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="44" ht="30" customHeight="1" s="1">
-      <ns0:c r="A44" s="0" t="n"/>
-      <ns0:c r="B44" s="2" t="n"/>
-      <ns0:c r="C44" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="45" ht="30" customHeight="1" s="1">
-      <ns0:c r="A45" s="0" t="n"/>
-      <ns0:c r="B45" s="2" t="n"/>
-      <ns0:c r="C45" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="46" ht="30" customHeight="1" s="1">
-      <ns0:c r="A46" s="0" t="n"/>
-      <ns0:c r="B46" s="0" t="n"/>
-      <ns0:c r="C46" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="47">
-      <ns0:c r="A47" t="inlineStr">
-        <ns0:is>
-          <ns0:t>explicitEnemyPlayerMinGap</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B47" t="inlineStr">
-        <ns0:is>
-          <ns0:t>显式超空间阵型与玩家舰体包络的最小发射空白，按战场高度比例；不改变普通阵型、船体尺寸或战斗数值。</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C47">
-        <ns0:v>0.12</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
+  <cols>
+    <col width="48" customWidth="1" style="1" min="1" max="1"/>
+    <col width="42" customWidth="1" style="1" min="2" max="2"/>
+    <col width="49" customWidth="1" style="1" min="3" max="3"/>
+    <col width="12.62963008880615" customWidth="1" style="1" min="13" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>des</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>para_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>这个配置的名字</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>配置的描述</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>配置的参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>如上</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>如上</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>如上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>startEquip</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>armour,laser</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>dmgReduce</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>护甲类型对应时，减少的伤害</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>movement</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>飞船的移动速度，单位是秒</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>autoCollectReduce</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>自动拾取时的损耗</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>backRange</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>死亡时后退距离</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>offlineMax</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>离线时长(h）</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>autoGenRes</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>30,2,5,40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>scientistCost</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>1.2,1|100,2|5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>hightechLimit</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>高科技投入AI的科研点数衰减</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>techPointGet</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>高科技点数获取</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>hightechCostGrowthLevel</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>高科技耗时指数增长阈值，当前等级超过此值后生效</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>jewelDrop</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>宝石碎片掉率</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>chronoParticlesPerSecond</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>每离线秒获得的超时空微粒</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>chronoDefaultSpeed</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>进入游戏及微粒不足时恢复的倍率</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>chronoSpeeds</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>倍率|每现实秒微粒消耗，逗号分隔</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>1|0,2|1,3|2,4|3,5|4,6|5,7|6,8|7,9|8,10|9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>reactorEnergyBase</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>反应炉1级总能源</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>reactorEnergyGrowth</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>反应炉每级总能源倍率</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>reactorUpgradeBase</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>反应炉1级升级铀消耗</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>reactorUpgradeGrowth</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>反应炉每级升级费用倍率</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>reactorBoostExponent</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>模块能源提升指数；提升百分比为分配能源的该次幂</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>reactorUraniumId</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>反应炉升级消耗的资源ID</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>reactorModules</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>反应炉可分配模块ID，逗号分隔</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>weapons,defence,smelting,condensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>reactorInitialLevel</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>新存档反应炉初始等级</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>reactorPercentScale</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>提升百分比换算分母</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>reactorAllocationStep</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>能源滑杆最小步长</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n"/>
+      <c r="B29" s="0" t="n"/>
+      <c r="C29" s="0" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n"/>
+      <c r="B30" s="0" t="n"/>
+      <c r="C30" s="0" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleFrigate</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>我方护卫舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleDestroyer</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>我方驱逐舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleCruiser</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>我方巡洋舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" s="1">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleBattleship</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>我方战列舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="1">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleHeavy_Battleship</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>我方重型战列舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1" s="1">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 1 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="1">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 2 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" s="1">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize3</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 3 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" s="1">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize4</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 4 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1" s="1">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize5</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 5 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1" s="1">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize6</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 6 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" s="1">
+      <c r="A42" s="0" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="0" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1" s="1">
+      <c r="A43" s="0" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="0" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1" s="1">
+      <c r="A44" s="0" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="0" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1" s="1">
+      <c r="A45" s="0" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="0" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1" s="1">
+      <c r="A46" s="0" t="n"/>
+      <c r="B46" s="0" t="n"/>
+      <c r="C46" s="0" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>explicitEnemyPlayerMinGap</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>显式超空间阵型与玩家舰体包络的最小发射空白，按战场高度比例；不改变普通阵型、船体尺寸或战斗数值。</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C22" s="0" t="n">
-        <v>1.35</v>
+        <v>1.30</v>
       </c>
     </row>
     <row r="23">

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1324,11 +1324,11 @@
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>反应炉每级总能源倍率</t>
+          <t>反应炉每级总能源倍率；同等级按当前配置统一计算</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">

--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="config" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1003,672 +1003,672 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:C47"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
-  <ns0:cols>
-    <ns0:col width="48" customWidth="1" style="1" min="1" max="1"/>
-    <ns0:col width="42" customWidth="1" style="1" min="2" max="2"/>
-    <ns0:col width="49" customWidth="1" style="1" min="3" max="3"/>
-    <ns0:col width="12.62963008880615" customWidth="1" style="1" min="13" max="14"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>des</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>para_1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>这个配置的名字</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>配置的描述</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>配置的参数</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>如上</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>如上</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C3" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>如上</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>startEquip</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>armour,laser</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>dmgReduce</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>护甲类型对应时，减少的伤害</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C5" s="0" t="n">
-        <ns0:v>0.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>movement</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>飞船的移动速度，单位是秒</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C6" s="0" t="n">
-        <ns0:v>50</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>autoCollectReduce</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B7" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>自动拾取时的损耗</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C7" s="0" t="n">
-        <ns0:v>0.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>backRange</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B8" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>死亡时后退距离</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C8" s="0" t="n">
-        <ns0:v>200</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>offlineMax</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B9" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>离线时长(h）</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C9" s="0" t="n">
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>autoGenRes</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B10" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C10" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>30,2,5,40</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11">
-      <ns0:c r="A11" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>scientistCost</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B11" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C11" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>1.2,1|100,2|5</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12">
-      <ns0:c r="A12" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>hightechLimit</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B12" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>高科技投入AI的科研点数衰减</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C12" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13">
-      <ns0:c r="A13" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>techPointGet</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B13" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>高科技点数获取</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C13" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14">
-      <ns0:c r="A14" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>hightechCostGrowthLevel</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B14" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>高科技耗时指数增长阈值，当前等级超过此值后生效</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C14" s="0" t="n">
-        <ns0:v>50</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15">
-      <ns0:c r="A15" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>jewelDrop</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B15" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>宝石碎片掉率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C15" s="0" t="n">
-        <ns0:v>0.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16">
-      <ns0:c r="A16" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>chronoParticlesPerSecond</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B16" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>每离线秒获得的超时空微粒</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C16" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17">
-      <ns0:c r="A17" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>chronoDefaultSpeed</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B17" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>进入游戏及微粒不足时恢复的倍率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C17" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18">
-      <ns0:c r="A18" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>chronoSpeeds</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B18" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>倍率|每现实秒微粒消耗，逗号分隔</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C18" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>1|0,2|1,3|2,4|3,5|4,6|5,7|6,8|7,9|8,10|9</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19">
-      <ns0:c r="A19" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorEnergyBase</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B19" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉1级总能源</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C19" s="0" t="n">
-        <ns0:v>100</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20">
-      <ns0:c r="A20" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorEnergyGrowth</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B20" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉每级总能源倍率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C20" s="0" t="n">
-        <ns0:v>1.06</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21">
-      <ns0:c r="A21" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorUpgradeBase</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B21" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉1级升级铀消耗</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C21" s="0" t="n">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22">
-      <ns0:c r="A22" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorUpgradeGrowth</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B22" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉每级升级费用倍率</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C22" s="0" t="n">
-        <ns0:v>1.35</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23">
-      <ns0:c r="A23" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorBoostExponent</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B23" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>模块能源提升指数；提升百分比为分配能源的该次幂</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C23" s="0" t="n">
-        <ns0:v>0.8</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24">
-      <ns0:c r="A24" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorUraniumId</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B24" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉升级消耗的资源ID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C24" s="0" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25">
-      <ns0:c r="A25" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorModules</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B25" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>反应炉可分配模块ID，逗号分隔</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C25" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>weapons,defence,smelting,condensation</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26">
-      <ns0:c r="A26" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorInitialLevel</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B26" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>新存档反应炉初始等级</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C26" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="27">
-      <ns0:c r="A27" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorPercentScale</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B27" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>提升百分比换算分母</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C27" s="0" t="n">
-        <ns0:v>100</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="28">
-      <ns0:c r="A28" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>reactorAllocationStep</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B28" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>能源滑杆最小步长</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C28" s="0" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="29">
-      <ns0:c r="A29" s="0" t="n"/>
-      <ns0:c r="B29" s="0" t="n"/>
-      <ns0:c r="C29" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="30">
-      <ns0:c r="A30" s="0" t="n"/>
-      <ns0:c r="B30" s="0" t="n"/>
-      <ns0:c r="C30" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="31">
-      <ns0:c r="A31" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleFrigate</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B31" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方护卫舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C31" s="0" t="n">
-        <ns0:v>1.3</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="32">
-      <ns0:c r="A32" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleDestroyer</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B32" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方驱逐舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C32" s="0" t="n">
-        <ns0:v>1.1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="33">
-      <ns0:c r="A33" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleCruiser</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B33" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方巡洋舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C33" s="0" t="n">
-        <ns0:v>1.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="34" ht="30" customHeight="1" s="1">
-      <ns0:c r="A34" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleBattleship</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B34" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方战列舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C34" s="0" t="n">
-        <ns0:v>1.3</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="35" ht="30" customHeight="1" s="1">
-      <ns0:c r="A35" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>playerVisualScaleHeavy_Battleship</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B35" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>我方重型战列舰显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C35" s="0" t="n">
-        <ns0:v>1.4</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="36" ht="30" customHeight="1" s="1">
-      <ns0:c r="A36" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B36" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 1 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C36" s="0" t="n">
-        <ns0:v>1.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="37" ht="30" customHeight="1" s="1">
-      <ns0:c r="A37" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize2</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B37" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 2 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C37" s="0" t="n">
-        <ns0:v>1.2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="38" ht="30" customHeight="1" s="1">
-      <ns0:c r="A38" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize3</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B38" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 3 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C38" s="0" t="n">
-        <ns0:v>1.4</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="39" ht="30" customHeight="1" s="1">
-      <ns0:c r="A39" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize4</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B39" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 4 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C39" s="0" t="n">
-        <ns0:v>1.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="40" ht="30" customHeight="1" s="1">
-      <ns0:c r="A40" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize5</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B40" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 5 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C40" s="0" t="n">
-        <ns0:v>1.5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="41" ht="30" customHeight="1" s="1">
-      <ns0:c r="A41" s="0" t="inlineStr">
-        <ns0:is>
-          <ns0:t>enemyVisualScaleSize6</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B41" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>敌方 size 6 显示倍率，仅影响舰体贴图</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C41" s="0" t="n">
-        <ns0:v>1.7</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="42" ht="30" customHeight="1" s="1">
-      <ns0:c r="A42" s="0" t="n"/>
-      <ns0:c r="B42" s="2" t="n"/>
-      <ns0:c r="C42" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="43" ht="30" customHeight="1" s="1">
-      <ns0:c r="A43" s="0" t="n"/>
-      <ns0:c r="B43" s="2" t="n"/>
-      <ns0:c r="C43" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="44" ht="30" customHeight="1" s="1">
-      <ns0:c r="A44" s="0" t="n"/>
-      <ns0:c r="B44" s="2" t="n"/>
-      <ns0:c r="C44" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="45" ht="30" customHeight="1" s="1">
-      <ns0:c r="A45" s="0" t="n"/>
-      <ns0:c r="B45" s="2" t="n"/>
-      <ns0:c r="C45" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="46" ht="30" customHeight="1" s="1">
-      <ns0:c r="A46" s="0" t="n"/>
-      <ns0:c r="B46" s="0" t="n"/>
-      <ns0:c r="C46" s="0" t="n"/>
-    </ns0:row>
-    <ns0:row r="47">
-      <ns0:c r="A47" t="inlineStr">
-        <ns0:is>
-          <ns0:t>explicitEnemyPlayerMinGap</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B47" t="inlineStr">
-        <ns0:is>
-          <ns0:t>显式超空间阵型与玩家舰体包络的最小发射空白，按战场高度比例；不改变普通阵型、船体尺寸或战斗数值。</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C47">
-        <ns0:v>0.12</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
+  <cols>
+    <col width="48" customWidth="1" style="1" min="1" max="1"/>
+    <col width="42" customWidth="1" style="1" min="2" max="2"/>
+    <col width="49" customWidth="1" style="1" min="3" max="3"/>
+    <col width="12.62963008880615" customWidth="1" style="1" min="13" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>des</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>para_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>这个配置的名字</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>配置的描述</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>配置的参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>如上</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>如上</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>如上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>startEquip</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>armour,laser</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>dmgReduce</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>护甲类型对应时，减少的伤害</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>movement</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>飞船的移动速度，单位是秒</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>autoCollectReduce</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>自动拾取时的损耗</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>backRange</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>死亡时后退距离</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>offlineMax</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>离线时长(h）</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>autoGenRes</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>画面上自动生成的资源,格式为生成间隔秒,种类,数量,移动速度.</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>30,2,5,40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>scientistCost</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>格式资源倍率,资源种类1|资源消耗1,资源种类2|资源消耗2....支持资源种类无限扩展</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>1.2,1|100,2|5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>hightechLimit</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>高科技投入AI的科研点数衰减</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>techPointGet</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>高科技点数获取</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>hightechCostGrowthLevel</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>高科技耗时指数增长阈值，当前等级超过此值后生效</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>jewelDrop</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>宝石碎片掉率</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>chronoParticlesPerSecond</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>每离线秒获得的超时空微粒</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>chronoDefaultSpeed</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>进入游戏及微粒不足时恢复的倍率</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>chronoSpeeds</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>倍率|每现实秒微粒消耗，逗号分隔</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>1|0,2|1,3|2,4|3,5|4,6|5,7|6,8|7,9|8,10|9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>reactorEnergyBase</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>反应炉1级总能源</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>reactorEnergyGrowth</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>反应炉每级总能源倍率</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>reactorUpgradeBase</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>反应炉1级升级铀消耗</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>reactorUpgradeGrowth</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>反应炉每级升级费用倍率</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>reactorBoostExponent</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>模块能源提升指数；提升百分比为分配能源的该次幂</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>reactorUraniumId</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>反应炉升级消耗的资源ID</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>reactorModules</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>反应炉可分配模块ID，逗号分隔</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>weapons,defence,smelting,condensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>reactorInitialLevel</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>新存档反应炉初始等级</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>reactorPercentScale</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>提升百分比换算分母</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>reactorAllocationStep</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>能源滑杆最小步长</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n"/>
+      <c r="B29" s="0" t="n"/>
+      <c r="C29" s="0" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n"/>
+      <c r="B30" s="0" t="n"/>
+      <c r="C30" s="0" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleFrigate</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>我方护卫舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleDestroyer</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>我方驱逐舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleCruiser</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>我方巡洋舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" s="1">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleBattleship</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>我方战列舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" s="1">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>playerVisualScaleHeavy_Battleship</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>我方重型战列舰显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1" s="1">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 1 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="1">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 2 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" s="1">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize3</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 3 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" s="1">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize4</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 4 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1" s="1">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize5</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 5 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1" s="1">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>enemyVisualScaleSize6</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>敌方 size 6 显示倍率，仅影响舰体贴图</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" s="1">
+      <c r="A42" s="0" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="0" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1" s="1">
+      <c r="A43" s="0" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="0" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1" s="1">
+      <c r="A44" s="0" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="0" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1" s="1">
+      <c r="A45" s="0" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="0" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1" s="1">
+      <c r="A46" s="0" t="n"/>
+      <c r="B46" s="0" t="n"/>
+      <c r="C46" s="0" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>explicitEnemyPlayerMinGap</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>显式超空间阵型与玩家舰体包络的最小发射空白，按战场高度比例；不改变普通阵型、船体尺寸或战斗数值。</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/space-battleship/config_excel/config.xlsx
+++ b/space-battleship/config_excel/config.xlsx
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888889312744141" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="48" customWidth="1" style="1" min="1" max="1"/>
@@ -1668,6 +1668,21 @@
         <v>0.12</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>equipmentSwitchCooldownSeconds</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>同一武器或防御槽位换装后再次换装的游戏秒数</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
